--- a/appointment_forms/048_hair_product_sample_testing_appointment_form--appointment_forms.xlsx
+++ b/appointment_forms/048_hair_product_sample_testing_appointment_form--appointment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'sample_type'}</t>
+          <t>sample_type</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Sample Type'}</t>
+          <t>Sample Type</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'hair_type'}</t>
+          <t>hair_type</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Hair Type'}</t>
+          <t>Hair Type</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'product_type'}</t>
+          <t>product_type</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Product Type'}</t>
+          <t>Product Type</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'tester'}</t>
+          <t>tester</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Tester'}</t>
+          <t>Tester</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'tester_name'}</t>
+          <t>tester_name</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Tester Name'}</t>
+          <t>Tester Name</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'tester_phone'}</t>
+          <t>tester_phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Tester Phone'}</t>
+          <t>Tester Phone</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'location'}</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Location'}</t>
+          <t>Location</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'staff'}</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'Staff'}</t>
+          <t>Staff</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'confirmed'}</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'Confirmed'}</t>
+          <t>Confirmed</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'not_confirmed'}</t>
+          <t>not_confirmed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'Not Confirmed'}</t>
+          <t>Not Confirmed</t>
         </is>
       </c>
     </row>
